--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/28,09,26 Останкино КИ и ЗПФ/машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ/Заказ ЛП_ПРС 04,10,26..xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/28,09,26 Останкино КИ и ЗПФ/машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ/Заказ ЛП_ПРС 04,10,26..xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\30,09 ПРС ЛП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\28,09,26 Останкино КИ и ЗПФ\машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898A821-7C97-40B8-923C-2DF4B551491D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33098949-4B69-4952-8B95-7DAF721DC240}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8688,7 +8688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1710"/>
@@ -8914,7 +8914,7 @@
       <c r="BN9" s="113"/>
       <c r="BO9" s="113"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -8928,7 +8928,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>4561</v>
       </c>
@@ -9017,7 +9017,7 @@
       <c r="BN11" s="114"/>
       <c r="BO11" s="114"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145">
         <v>7536</v>
       </c>
@@ -9106,7 +9106,7 @@
       <c r="BN12" s="114"/>
       <c r="BO12" s="114"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>5851</v>
       </c>
@@ -9195,7 +9195,7 @@
       <c r="BN13" s="114"/>
       <c r="BO13" s="114"/>
     </row>
-    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>4813</v>
       </c>
@@ -9284,7 +9284,7 @@
       <c r="BN14" s="114"/>
       <c r="BO14" s="114"/>
     </row>
-    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57">
         <v>4574</v>
       </c>
@@ -9373,7 +9373,7 @@
       <c r="BN15" s="114"/>
       <c r="BO15" s="114"/>
     </row>
-    <row r="16" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>4063</v>
       </c>
@@ -9444,7 +9444,7 @@
       <c r="AW16" s="115"/>
       <c r="AX16" s="115"/>
     </row>
-    <row r="17" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57">
         <v>6220</v>
       </c>
@@ -9477,7 +9477,7 @@
       <c r="J17" s="29"/>
       <c r="L17" s="115"/>
     </row>
-    <row r="18" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57">
         <v>6498</v>
       </c>
@@ -9510,7 +9510,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="115"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>6861</v>
       </c>
@@ -9543,7 +9543,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="115"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57">
         <v>6862</v>
       </c>
@@ -9576,7 +9576,7 @@
       <c r="J20" s="29"/>
       <c r="L20" s="115"/>
     </row>
-    <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="145">
         <v>7539</v>
       </c>
@@ -9609,7 +9609,7 @@
       <c r="J21" s="60"/>
       <c r="L21" s="115"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>7334</v>
       </c>
@@ -9642,7 +9642,7 @@
       <c r="J22" s="29"/>
       <c r="L22" s="115"/>
     </row>
-    <row r="23" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="57">
         <v>6325</v>
       </c>
@@ -9675,7 +9675,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="115"/>
     </row>
-    <row r="24" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57">
         <v>8014</v>
       </c>
@@ -9764,7 +9764,7 @@
       <c r="BN24" s="115"/>
       <c r="BO24" s="115"/>
     </row>
-    <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="145">
         <v>7632</v>
       </c>
@@ -9853,7 +9853,7 @@
       <c r="BN25" s="115"/>
       <c r="BO25" s="115"/>
     </row>
-    <row r="26" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="145">
         <v>7523</v>
       </c>
@@ -9942,7 +9942,7 @@
       <c r="BN26" s="115"/>
       <c r="BO26" s="115"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="138">
         <v>6340</v>
       </c>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="L27" s="115"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="138">
         <v>6341</v>
       </c>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="L28" s="115"/>
     </row>
-    <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57">
         <v>6333</v>
       </c>
@@ -10078,7 +10078,7 @@
       <c r="J30" s="60"/>
       <c r="L30" s="115"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="57">
         <v>7343</v>
       </c>
@@ -10111,7 +10111,7 @@
       <c r="J31" s="29"/>
       <c r="L31" s="115"/>
     </row>
-    <row r="32" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="57">
         <v>6797</v>
       </c>
@@ -10289,7 +10289,7 @@
       <c r="BN33" s="115"/>
       <c r="BO33" s="115"/>
     </row>
-    <row r="34" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="148">
         <v>7514</v>
       </c>
@@ -10377,7 +10377,7 @@
       <c r="BN34" s="115"/>
       <c r="BO34" s="115"/>
     </row>
-    <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="148">
         <v>7518</v>
       </c>
@@ -10465,7 +10465,7 @@
       <c r="BN35" s="115"/>
       <c r="BO35" s="115"/>
     </row>
-    <row r="36" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
         <v>104</v>
       </c>
@@ -10482,7 +10482,7 @@
       <c r="J36" s="44"/>
       <c r="L36" s="115"/>
     </row>
-    <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="57">
         <v>6767</v>
       </c>
@@ -10568,7 +10568,7 @@
       <c r="BN37" s="115"/>
       <c r="BO37" s="115"/>
     </row>
-    <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="57">
         <v>6761</v>
       </c>
@@ -10654,7 +10654,7 @@
       <c r="BN38" s="115"/>
       <c r="BO38" s="115"/>
     </row>
-    <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="57">
         <v>6764</v>
       </c>
@@ -10740,7 +10740,7 @@
       <c r="BN39" s="115"/>
       <c r="BO39" s="115"/>
     </row>
-    <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="57">
         <v>6254</v>
       </c>
@@ -10826,7 +10826,7 @@
       <c r="BN40" s="115"/>
       <c r="BO40" s="115"/>
     </row>
-    <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="57">
         <v>7075</v>
       </c>
@@ -10912,7 +10912,7 @@
       <c r="BN41" s="115"/>
       <c r="BO41" s="115"/>
     </row>
-    <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="57">
         <v>7083</v>
       </c>
@@ -10998,7 +10998,7 @@
       <c r="BN42" s="115"/>
       <c r="BO42" s="115"/>
     </row>
-    <row r="43" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="57">
         <v>6829</v>
       </c>
@@ -11084,7 +11084,7 @@
       <c r="BN43" s="115"/>
       <c r="BO43" s="115"/>
     </row>
-    <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="57">
         <v>7070</v>
       </c>
@@ -11170,7 +11170,7 @@
       <c r="BN44" s="115"/>
       <c r="BO44" s="115"/>
     </row>
-    <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="57">
         <v>7076</v>
       </c>
@@ -11256,7 +11256,7 @@
       <c r="BN45" s="115"/>
       <c r="BO45" s="115"/>
     </row>
-    <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="57">
         <v>7271</v>
       </c>
@@ -11342,7 +11342,7 @@
       <c r="BN46" s="115"/>
       <c r="BO46" s="115"/>
     </row>
-    <row r="47" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="57">
         <v>6303</v>
       </c>
@@ -11428,7 +11428,7 @@
       <c r="BN47" s="115"/>
       <c r="BO47" s="115"/>
     </row>
-    <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="57">
         <v>6661</v>
       </c>
@@ -11514,7 +11514,7 @@
       <c r="BN48" s="115"/>
       <c r="BO48" s="115"/>
     </row>
-    <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="57">
         <v>6759</v>
       </c>
@@ -11600,7 +11600,7 @@
       <c r="BN49" s="115"/>
       <c r="BO49" s="115"/>
     </row>
-    <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="57">
         <v>6762</v>
       </c>
@@ -11686,7 +11686,7 @@
       <c r="BN50" s="115"/>
       <c r="BO50" s="115"/>
     </row>
-    <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="57">
         <v>6765</v>
       </c>
@@ -11772,7 +11772,7 @@
       <c r="BN51" s="115"/>
       <c r="BO51" s="115"/>
     </row>
-    <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="57">
         <v>7074</v>
       </c>
@@ -11858,7 +11858,7 @@
       <c r="BN52" s="115"/>
       <c r="BO52" s="115"/>
     </row>
-    <row r="53" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="57">
         <v>7123</v>
       </c>
@@ -11944,7 +11944,7 @@
       <c r="BN53" s="115"/>
       <c r="BO53" s="115"/>
     </row>
-    <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="57">
         <v>5819</v>
       </c>
@@ -12030,7 +12030,7 @@
       <c r="BN54" s="115"/>
       <c r="BO54" s="115"/>
     </row>
-    <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="57">
         <v>6475</v>
       </c>
@@ -12116,7 +12116,7 @@
       <c r="BN55" s="115"/>
       <c r="BO55" s="115"/>
     </row>
-    <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="138">
         <v>7284</v>
       </c>
@@ -12293,7 +12293,7 @@
       <c r="BN57" s="115"/>
       <c r="BO57" s="115"/>
     </row>
-    <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="57">
         <v>7601</v>
       </c>
@@ -12379,7 +12379,7 @@
       <c r="BN58" s="115"/>
       <c r="BO58" s="115"/>
     </row>
-    <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="138">
         <v>7371</v>
       </c>
@@ -12467,7 +12467,7 @@
       <c r="BN59" s="115"/>
       <c r="BO59" s="115"/>
     </row>
-    <row r="60" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="57">
         <v>6837</v>
       </c>
@@ -12553,7 +12553,7 @@
       <c r="BN60" s="115"/>
       <c r="BO60" s="115"/>
     </row>
-    <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="57">
         <v>7080</v>
       </c>
@@ -12583,7 +12583,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="115"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="57">
         <v>6724</v>
       </c>
@@ -12646,7 +12646,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="115"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="138">
         <v>6713</v>
       </c>
@@ -12678,7 +12678,7 @@
       </c>
       <c r="L64" s="115"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="57">
         <v>7490</v>
       </c>
@@ -12743,7 +12743,7 @@
       <c r="J66" s="29"/>
       <c r="L66" s="115"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="57">
         <v>6602</v>
       </c>
@@ -12773,7 +12773,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="115"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="145">
         <v>7040</v>
       </c>
@@ -12803,7 +12803,7 @@
       <c r="J68" s="60"/>
       <c r="L68" s="115"/>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="138">
         <v>7521</v>
       </c>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="L69" s="115"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="57">
         <v>7073</v>
       </c>
@@ -12898,7 +12898,7 @@
       <c r="J71" s="29"/>
       <c r="L71" s="115"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="57">
         <v>6616</v>
       </c>
@@ -12928,7 +12928,7 @@
       <c r="J72" s="29"/>
       <c r="L72" s="115"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="57">
         <v>7044</v>
       </c>
@@ -12958,7 +12958,7 @@
       <c r="J73" s="29"/>
       <c r="L73" s="115"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="138">
         <v>7385</v>
       </c>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="L74" s="115"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="138">
         <v>7460</v>
       </c>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="L75" s="115"/>
     </row>
-    <row r="76" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>104</v>
       </c>
@@ -13039,7 +13039,7 @@
       <c r="J76" s="44"/>
       <c r="L76" s="115"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A77" s="57">
         <v>6527</v>
       </c>
@@ -13069,7 +13069,7 @@
       <c r="J77" s="60"/>
       <c r="L77" s="115"/>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="57">
         <v>6550</v>
       </c>
@@ -13099,7 +13099,7 @@
       <c r="J78" s="29"/>
       <c r="L78" s="115"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="57">
         <v>6549</v>
       </c>
@@ -13129,7 +13129,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="115"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="57">
         <v>7001</v>
       </c>
@@ -13159,7 +13159,7 @@
       <c r="J80" s="29"/>
       <c r="L80" s="115"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="57">
         <v>6608</v>
       </c>
@@ -13189,7 +13189,7 @@
       <c r="J81" s="29"/>
       <c r="L81" s="115"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="57">
         <v>7059</v>
       </c>
@@ -13219,7 +13219,7 @@
       <c r="J82" s="29"/>
       <c r="L82" s="115"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="57">
         <v>6609</v>
       </c>
@@ -13249,7 +13249,7 @@
       <c r="J83" s="29"/>
       <c r="L83" s="115"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
         <v>104</v>
       </c>
@@ -13266,7 +13266,7 @@
       <c r="J84" s="44"/>
       <c r="L84" s="115"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A85" s="145">
         <v>7564</v>
       </c>
@@ -13296,7 +13296,7 @@
       <c r="J85" s="60"/>
       <c r="L85" s="115"/>
     </row>
-    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="57">
         <v>7133</v>
       </c>
@@ -13326,7 +13326,7 @@
       <c r="J86" s="60"/>
       <c r="L86" s="115"/>
     </row>
-    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="57">
         <v>6946</v>
       </c>
@@ -13356,7 +13356,7 @@
       <c r="J87" s="29"/>
       <c r="L87" s="115"/>
     </row>
-    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="57">
         <v>7132</v>
       </c>
@@ -13386,7 +13386,7 @@
       <c r="J88" s="60"/>
       <c r="L88" s="115"/>
     </row>
-    <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="57">
         <v>5544</v>
       </c>
@@ -13416,7 +13416,7 @@
       <c r="J89" s="60"/>
       <c r="L89" s="115"/>
     </row>
-    <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="57">
         <v>7149</v>
       </c>
@@ -13446,7 +13446,7 @@
       <c r="J90" s="60"/>
       <c r="L90" s="115"/>
     </row>
-    <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="57">
         <v>7157</v>
       </c>
@@ -13476,7 +13476,7 @@
       <c r="J91" s="60"/>
       <c r="L91" s="115"/>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="57">
         <v>7166</v>
       </c>
@@ -13506,7 +13506,7 @@
       <c r="J92" s="60"/>
       <c r="L92" s="115"/>
     </row>
-    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="145">
         <v>7603</v>
       </c>
@@ -13536,7 +13536,7 @@
       <c r="J93" s="60"/>
       <c r="L93" s="115"/>
     </row>
-    <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="138">
         <v>7489</v>
       </c>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="L94" s="115"/>
     </row>
-    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="57">
         <v>6807</v>
       </c>
@@ -13598,7 +13598,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="115"/>
     </row>
-    <row r="96" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="57">
         <v>6787</v>
       </c>
@@ -13694,7 +13694,7 @@
       <c r="J98" s="29"/>
       <c r="L98" s="115"/>
     </row>
-    <row r="99" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="57">
         <v>7233</v>
       </c>
@@ -13790,7 +13790,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="115"/>
     </row>
-    <row r="102" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="57">
         <v>7232</v>
       </c>
@@ -13820,7 +13820,7 @@
       <c r="J102" s="50"/>
       <c r="L102" s="115"/>
     </row>
-    <row r="103" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="148">
         <v>7156</v>
       </c>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="L103" s="115"/>
     </row>
-    <row r="104" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="148">
         <v>7710</v>
       </c>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="L104" s="115"/>
     </row>
-    <row r="105" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="148">
         <v>7562</v>
       </c>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="L105" s="115"/>
     </row>
-    <row r="106" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="148">
         <v>7516</v>
       </c>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="L106" s="115"/>
     </row>
-    <row r="107" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="148">
         <v>7513</v>
       </c>
@@ -14013,7 +14013,7 @@
       <c r="J108" s="50"/>
       <c r="L108" s="115"/>
     </row>
-    <row r="109" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="57">
         <v>7238</v>
       </c>
@@ -14046,7 +14046,7 @@
       <c r="J109" s="50"/>
       <c r="L109" s="115"/>
     </row>
-    <row r="110" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="138">
         <v>7237</v>
       </c>
@@ -14114,7 +14114,7 @@
       <c r="J111" s="50"/>
       <c r="L111" s="115"/>
     </row>
-    <row r="112" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="138">
         <v>7332</v>
       </c>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="L112" s="115"/>
     </row>
-    <row r="113" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="138">
         <v>7333</v>
       </c>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="L113" s="115"/>
     </row>
-    <row r="114" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="145">
         <v>7608</v>
       </c>
@@ -14208,7 +14208,7 @@
       <c r="J114" s="60"/>
       <c r="L114" s="115"/>
     </row>
-    <row r="115" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="138">
         <v>7610</v>
       </c>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="L115" s="115"/>
     </row>
-    <row r="116" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
         <v>104</v>
       </c>
@@ -14313,7 +14313,7 @@
       <c r="BN116" s="115"/>
       <c r="BO116" s="115"/>
     </row>
-    <row r="117" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A117" s="57">
         <v>614</v>
       </c>
@@ -14399,7 +14399,7 @@
       <c r="BN117" s="115"/>
       <c r="BO117" s="115"/>
     </row>
-    <row r="118" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="57">
         <v>3287</v>
       </c>
@@ -14485,7 +14485,7 @@
       <c r="BN118" s="115"/>
       <c r="BO118" s="115"/>
     </row>
-    <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="168">
         <v>5708</v>
       </c>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="L119" s="115"/>
     </row>
-    <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="171">
         <v>7700</v>
       </c>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="L120" s="115"/>
     </row>
-    <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="57">
         <v>4117</v>
       </c>
@@ -14579,7 +14579,7 @@
       <c r="J121" s="29"/>
       <c r="L121" s="115"/>
     </row>
-    <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="57">
         <v>7316</v>
       </c>
@@ -14609,7 +14609,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="115"/>
     </row>
-    <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="57">
         <v>7317</v>
       </c>
@@ -14639,7 +14639,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="115"/>
     </row>
-    <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="57">
         <v>7143</v>
       </c>
@@ -14669,7 +14669,7 @@
       <c r="J124" s="29"/>
       <c r="L124" s="115"/>
     </row>
-    <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="168">
         <v>7147</v>
       </c>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="L125" s="115"/>
     </row>
-    <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="57">
         <v>7456</v>
       </c>
@@ -14731,7 +14731,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="115"/>
     </row>
-    <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="57">
         <v>7318</v>
       </c>
@@ -14794,7 +14794,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="115"/>
     </row>
-    <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="57">
         <v>7364</v>
       </c>
@@ -14824,7 +14824,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="115"/>
     </row>
-    <row r="130" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="57">
         <v>7383</v>
       </c>
@@ -14920,7 +14920,7 @@
       <c r="J132" s="29"/>
       <c r="L132" s="115"/>
     </row>
-    <row r="133" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="57">
         <v>6937</v>
       </c>
@@ -15016,7 +15016,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="115"/>
     </row>
-    <row r="136" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="57">
         <v>6832</v>
       </c>
@@ -15046,7 +15046,7 @@
       <c r="J136" s="29"/>
       <c r="L136" s="115"/>
     </row>
-    <row r="137" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="57">
         <v>7299</v>
       </c>
@@ -15076,7 +15076,7 @@
       <c r="J137" s="29"/>
       <c r="L137" s="115"/>
     </row>
-    <row r="138" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="57">
         <v>7386</v>
       </c>
@@ -15172,7 +15172,7 @@
       <c r="J140" s="29"/>
       <c r="L140" s="115"/>
     </row>
-    <row r="141" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="145">
         <v>7613</v>
       </c>
@@ -15301,7 +15301,7 @@
       <c r="J144" s="29"/>
       <c r="L144" s="115"/>
     </row>
-    <row r="145" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="138">
         <v>6834</v>
       </c>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="L145" s="115"/>
     </row>
-    <row r="146" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="138">
         <v>6965</v>
       </c>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="L146" s="115"/>
     </row>
-    <row r="147" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="138">
         <v>6557</v>
       </c>
@@ -15397,7 +15397,7 @@
       </c>
       <c r="L147" s="115"/>
     </row>
-    <row r="148" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="145">
         <v>7626</v>
       </c>
@@ -15427,7 +15427,7 @@
       <c r="J148" s="60"/>
       <c r="L148" s="115"/>
     </row>
-    <row r="149" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="48" t="s">
         <v>104</v>
       </c>
@@ -15444,7 +15444,7 @@
       <c r="J149" s="44"/>
       <c r="L149" s="115"/>
     </row>
-    <row r="150" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A150" s="168">
         <v>6470</v>
       </c>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="L150" s="115"/>
     </row>
-    <row r="151" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="171">
         <v>7726</v>
       </c>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="L151" s="115"/>
     </row>
-    <row r="152" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="176">
         <v>6495</v>
       </c>
@@ -15596,7 +15596,7 @@
       <c r="BN152" s="115"/>
       <c r="BO152" s="115"/>
     </row>
-    <row r="153" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="171">
         <v>7725</v>
       </c>
@@ -15684,7 +15684,7 @@
       <c r="BN153" s="115"/>
       <c r="BO153" s="115"/>
     </row>
-    <row r="154" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="57">
         <v>5452</v>
       </c>
@@ -15770,7 +15770,7 @@
       <c r="BN154" s="115"/>
       <c r="BO154" s="115"/>
     </row>
-    <row r="155" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="57">
         <v>6866</v>
       </c>
@@ -15856,7 +15856,7 @@
       <c r="BN155" s="115"/>
       <c r="BO155" s="115"/>
     </row>
-    <row r="156" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="57">
         <v>6025</v>
       </c>
@@ -15942,7 +15942,7 @@
       <c r="BN156" s="115"/>
       <c r="BO156" s="115"/>
     </row>
-    <row r="157" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="57">
         <v>4584</v>
       </c>
@@ -16206,7 +16206,7 @@
       <c r="BN159" s="115"/>
       <c r="BO159" s="115"/>
     </row>
-    <row r="160" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="57">
         <v>7377</v>
       </c>
@@ -16292,7 +16292,7 @@
       <c r="BN160" s="115"/>
       <c r="BO160" s="115"/>
     </row>
-    <row r="161" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="176">
         <v>6925</v>
       </c>
@@ -16380,7 +16380,7 @@
       <c r="BN161" s="115"/>
       <c r="BO161" s="115"/>
     </row>
-    <row r="162" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="180">
         <v>7723</v>
       </c>
@@ -16468,7 +16468,7 @@
       <c r="BN162" s="115"/>
       <c r="BO162" s="115"/>
     </row>
-    <row r="163" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="168">
         <v>7647</v>
       </c>
@@ -16646,7 +16646,7 @@
       <c r="BN164" s="115"/>
       <c r="BO164" s="115"/>
     </row>
-    <row r="165" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="168">
         <v>7651</v>
       </c>
@@ -16734,7 +16734,7 @@
       <c r="BN165" s="115"/>
       <c r="BO165" s="115"/>
     </row>
-    <row r="166" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="171">
         <v>7731</v>
       </c>
@@ -16822,7 +16822,7 @@
       <c r="BN166" s="115"/>
       <c r="BO166" s="115"/>
     </row>
-    <row r="167" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="48" t="s">
         <v>104</v>
       </c>
@@ -16895,7 +16895,7 @@
       <c r="BN167" s="115"/>
       <c r="BO167" s="115"/>
     </row>
-    <row r="168" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="145">
         <v>7485</v>
       </c>
@@ -16981,7 +16981,7 @@
       <c r="BN168" s="115"/>
       <c r="BO168" s="115"/>
     </row>
-    <row r="169" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="48" t="s">
         <v>104</v>
       </c>
@@ -16998,7 +16998,7 @@
       <c r="J169" s="44"/>
       <c r="L169" s="115"/>
     </row>
-    <row r="170" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A170" s="57">
         <v>6620</v>
       </c>
@@ -17028,7 +17028,7 @@
       <c r="J170" s="29"/>
       <c r="L170" s="115"/>
     </row>
-    <row r="171" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="57">
         <v>7187</v>
       </c>
@@ -17058,7 +17058,7 @@
       <c r="J171" s="29"/>
       <c r="L171" s="115"/>
     </row>
-    <row r="172" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="145">
         <v>6008</v>
       </c>
@@ -17154,7 +17154,7 @@
       <c r="J174" s="29"/>
       <c r="L174" s="115"/>
     </row>
-    <row r="175" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="57">
         <v>6279</v>
       </c>
@@ -17187,7 +17187,7 @@
       <c r="J175" s="29"/>
       <c r="L175" s="115"/>
     </row>
-    <row r="176" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="148">
         <v>6929</v>
       </c>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="L176" s="115"/>
     </row>
-    <row r="177" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="57">
         <v>7092</v>
       </c>
@@ -17249,7 +17249,7 @@
       <c r="J177" s="29"/>
       <c r="L177" s="115"/>
     </row>
-    <row r="178" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="138">
         <v>6448</v>
       </c>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="L178" s="115"/>
     </row>
-    <row r="179" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="57">
         <v>6754</v>
       </c>
@@ -17311,7 +17311,7 @@
       <c r="J179" s="29"/>
       <c r="L179" s="115"/>
     </row>
-    <row r="180" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="57">
         <v>6208</v>
       </c>
@@ -17341,7 +17341,7 @@
       <c r="J180" s="29"/>
       <c r="L180" s="115"/>
     </row>
-    <row r="181" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="57">
         <v>6228</v>
       </c>
@@ -17371,7 +17371,7 @@
       <c r="J181" s="29"/>
       <c r="L181" s="115"/>
     </row>
-    <row r="182" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="145">
         <v>7612</v>
       </c>
@@ -17401,7 +17401,7 @@
       <c r="J182" s="60"/>
       <c r="L182" s="115"/>
     </row>
-    <row r="183" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="48" t="s">
         <v>104</v>
       </c>
@@ -17418,7 +17418,7 @@
       <c r="J183" s="44"/>
       <c r="L183" s="115"/>
     </row>
-    <row r="184" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A184" s="148">
         <v>7344</v>
       </c>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="L184" s="115"/>
     </row>
-    <row r="185" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="148">
         <v>7345</v>
       </c>
@@ -32738,7 +32738,27 @@
       <c r="J1710" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J186" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J186" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="100"/>
+        <filter val="120"/>
+        <filter val="150"/>
+        <filter val="180"/>
+        <filter val="220"/>
+        <filter val="240"/>
+        <filter val="30"/>
+        <filter val="300"/>
+        <filter val="4 520,00"/>
+        <filter val="460"/>
+        <filter val="50"/>
+        <filter val="60"/>
+        <filter val="70"/>
+        <filter val="80"/>
+        <filter val="90"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
